--- a/shipClassTests/testResults/SensedComp_GoodSensors_example.xlsx
+++ b/shipClassTests/testResults/SensedComp_GoodSensors_example.xlsx
@@ -78,42 +78,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -134,13 +104,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -502,7 +472,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3">
         <f>IF(B2 = F2, 1, 0)</f>
@@ -561,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -573,7 +543,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4">
         <v>2</v>
@@ -592,7 +562,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -604,16 +574,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3">
         <f>IF(B5 = F5, 1, 0)</f>
@@ -629,28 +599,28 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
         <f>IF(B6 = F6, 1, 0)</f>
@@ -666,28 +636,28 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3">
         <f>IF(B7 = F7, 1, 0)</f>
@@ -703,7 +673,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -712,16 +682,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4">
         <v>2</v>
@@ -740,7 +710,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -749,16 +719,16 @@
         <v>1</v>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="4">
         <v>2</v>
@@ -777,7 +747,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -786,16 +756,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" s="4">
         <v>2</v>
@@ -814,22 +784,22 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -860,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -872,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <f>IF(B12 = F12, 1, 0)</f>
@@ -928,25 +898,25 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3">
         <f>IF(B14 = F14, 1, 0)</f>
@@ -971,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -983,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3">
         <f>IF(B15 = F15, 1, 0)</f>
@@ -1005,7 +975,7 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4">
         <v>1</v>
@@ -1017,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
@@ -1045,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1057,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3">
         <f>IF(B17 = F17, 1, 0)</f>
@@ -1079,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -1091,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
@@ -1153,10 +1123,10 @@
         <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1165,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="3">
         <f>IF(B20 = F20, 1, 0)</f>
@@ -1193,7 +1163,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1205,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3">
         <f>IF(B21 = F21, 1, 0)</f>
@@ -1227,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4">
         <v>1</v>
@@ -1239,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -1267,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1279,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="3">
         <f>IF(B23 = F23, 1, 0)</f>
@@ -1338,10 +1308,10 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1350,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="3">
         <f>IF(B25 = F25, 1, 0)</f>

--- a/shipClassTests/testResults/SensedComp_GoodSensors_example.xlsx
+++ b/shipClassTests/testResults/SensedComp_GoodSensors_example.xlsx
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>2</v>
